--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118366628</v>
+        <v>118366020</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>90749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,38 +816,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497686</v>
+        <v>497811</v>
       </c>
       <c r="R3" t="n">
-        <v>6914152</v>
+        <v>6914303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,6 +901,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -916,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118365520</v>
+        <v>118365298</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,38 +932,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497776</v>
+        <v>497786</v>
       </c>
       <c r="R4" t="n">
-        <v>6914369</v>
+        <v>6914375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118366870</v>
+        <v>118366558</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,21 +1057,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497685</v>
+        <v>497765</v>
       </c>
       <c r="R5" t="n">
-        <v>6914149</v>
+        <v>6914163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118366558</v>
+        <v>118366174</v>
       </c>
       <c r="B6" t="n">
         <v>78221</v>
@@ -1180,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497765</v>
+        <v>497751</v>
       </c>
       <c r="R6" t="n">
-        <v>6914163</v>
+        <v>6914252</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118365427</v>
+        <v>118366237</v>
       </c>
       <c r="B7" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497763</v>
+        <v>497770</v>
       </c>
       <c r="R7" t="n">
-        <v>6914373</v>
+        <v>6914222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118366174</v>
+        <v>118365520</v>
       </c>
       <c r="B8" t="n">
-        <v>78221</v>
+        <v>91779</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497751</v>
+        <v>497776</v>
       </c>
       <c r="R8" t="n">
-        <v>6914252</v>
+        <v>6914369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118366889</v>
+        <v>118366628</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1516,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497668</v>
+        <v>497686</v>
       </c>
       <c r="R9" t="n">
-        <v>6914135</v>
+        <v>6914152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1700,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118366103</v>
+        <v>118366889</v>
       </c>
       <c r="B11" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,21 +1729,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1753,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497818</v>
+        <v>497668</v>
       </c>
       <c r="R11" t="n">
-        <v>6914247</v>
+        <v>6914135</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118365226</v>
+        <v>118366103</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,47 +1837,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497780</v>
+        <v>497818</v>
       </c>
       <c r="R12" t="n">
-        <v>6914401</v>
+        <v>6914247</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118366020</v>
+        <v>118365220</v>
       </c>
       <c r="B13" t="n">
-        <v>90749</v>
+        <v>97846</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,37 +1953,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497811</v>
+        <v>497793</v>
       </c>
       <c r="R13" t="n">
-        <v>6914303</v>
+        <v>6914389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,7 +2040,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2049,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118365298</v>
+        <v>118365427</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,47 +2070,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497786</v>
+        <v>497763</v>
       </c>
       <c r="R14" t="n">
-        <v>6914375</v>
+        <v>6914373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118365220</v>
+        <v>118365226</v>
       </c>
       <c r="B15" t="n">
         <v>97846</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497793</v>
+        <v>497780</v>
       </c>
       <c r="R15" t="n">
-        <v>6914389</v>
+        <v>6914401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118366237</v>
+        <v>118366870</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497770</v>
+        <v>497685</v>
       </c>
       <c r="R16" t="n">
-        <v>6914222</v>
+        <v>6914149</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118366020</v>
+        <v>118365298</v>
       </c>
       <c r="B3" t="n">
-        <v>90749</v>
+        <v>97846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,37 +820,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497811</v>
+        <v>497786</v>
       </c>
       <c r="R3" t="n">
-        <v>6914303</v>
+        <v>6914375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +907,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118365298</v>
+        <v>118366558</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,47 +937,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497786</v>
+        <v>497765</v>
       </c>
       <c r="R4" t="n">
-        <v>6914375</v>
+        <v>6914163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118366558</v>
+        <v>118366174</v>
       </c>
       <c r="B5" t="n">
         <v>78221</v>
@@ -1081,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497765</v>
+        <v>497751</v>
       </c>
       <c r="R5" t="n">
-        <v>6914163</v>
+        <v>6914252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118366174</v>
+        <v>118366237</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497751</v>
+        <v>497770</v>
       </c>
       <c r="R6" t="n">
-        <v>6914252</v>
+        <v>6914222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1265,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118366237</v>
+        <v>118366020</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,38 +1273,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497770</v>
+        <v>497811</v>
       </c>
       <c r="R7" t="n">
-        <v>6914222</v>
+        <v>6914303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,6 +1358,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118365298</v>
+        <v>118366628</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,47 +816,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497786</v>
+        <v>497686</v>
       </c>
       <c r="R3" t="n">
-        <v>6914375</v>
+        <v>6914152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -925,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118366558</v>
+        <v>118365220</v>
       </c>
       <c r="B4" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,38 +928,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497765</v>
+        <v>497793</v>
       </c>
       <c r="R4" t="n">
-        <v>6914163</v>
+        <v>6914389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118366174</v>
+        <v>118366558</v>
       </c>
       <c r="B5" t="n">
         <v>78221</v>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497751</v>
+        <v>497765</v>
       </c>
       <c r="R5" t="n">
-        <v>6914252</v>
+        <v>6914163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118366237</v>
+        <v>118366103</v>
       </c>
       <c r="B6" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1165,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497770</v>
+        <v>497818</v>
       </c>
       <c r="R6" t="n">
-        <v>6914222</v>
+        <v>6914247</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118366020</v>
+        <v>118366889</v>
       </c>
       <c r="B7" t="n">
-        <v>90749</v>
+        <v>79073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,41 +1273,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497811</v>
+        <v>497668</v>
       </c>
       <c r="R7" t="n">
-        <v>6914303</v>
+        <v>6914135</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1355,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1489,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118366628</v>
+        <v>118366237</v>
       </c>
       <c r="B9" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497686</v>
+        <v>497770</v>
       </c>
       <c r="R9" t="n">
-        <v>6914152</v>
+        <v>6914222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118366859</v>
+        <v>118366174</v>
       </c>
       <c r="B10" t="n">
         <v>78221</v>
@@ -1641,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497691</v>
+        <v>497751</v>
       </c>
       <c r="R10" t="n">
-        <v>6914141</v>
+        <v>6914252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118366889</v>
+        <v>118366020</v>
       </c>
       <c r="B11" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,38 +1721,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497668</v>
+        <v>497811</v>
       </c>
       <c r="R11" t="n">
-        <v>6914135</v>
+        <v>6914303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,6 +1806,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118366103</v>
+        <v>118365298</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,38 +1837,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497818</v>
+        <v>497786</v>
       </c>
       <c r="R12" t="n">
-        <v>6914247</v>
+        <v>6914375</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118365220</v>
+        <v>118366859</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,47 +1958,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497793</v>
+        <v>497691</v>
       </c>
       <c r="R13" t="n">
-        <v>6914389</v>
+        <v>6914141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118365427</v>
+        <v>118365226</v>
       </c>
       <c r="B14" t="n">
-        <v>78129</v>
+        <v>97846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,38 +2070,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497763</v>
+        <v>497780</v>
       </c>
       <c r="R14" t="n">
-        <v>6914373</v>
+        <v>6914401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2170,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118365226</v>
+        <v>118365427</v>
       </c>
       <c r="B15" t="n">
-        <v>97846</v>
+        <v>78129</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,47 +2191,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497780</v>
+        <v>497763</v>
       </c>
       <c r="R15" t="n">
-        <v>6914401</v>
+        <v>6914373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118366628</v>
+        <v>118366889</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>79080</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497686</v>
+        <v>497668</v>
       </c>
       <c r="R3" t="n">
-        <v>6914152</v>
+        <v>6914135</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118365220</v>
+        <v>118366859</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,47 +928,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497793</v>
+        <v>497691</v>
       </c>
       <c r="R4" t="n">
-        <v>6914389</v>
+        <v>6914141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118366558</v>
+        <v>118366103</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>78228</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497765</v>
+        <v>497818</v>
       </c>
       <c r="R5" t="n">
-        <v>6914163</v>
+        <v>6914247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118366103</v>
+        <v>118365427</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>78136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497818</v>
+        <v>497763</v>
       </c>
       <c r="R6" t="n">
-        <v>6914247</v>
+        <v>6914373</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118366889</v>
+        <v>118365220</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,38 +1264,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497668</v>
+        <v>497793</v>
       </c>
       <c r="R7" t="n">
-        <v>6914135</v>
+        <v>6914389</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118365520</v>
+        <v>118366558</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>78228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1385,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497776</v>
+        <v>497765</v>
       </c>
       <c r="R8" t="n">
-        <v>6914369</v>
+        <v>6914163</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118366237</v>
+        <v>118366628</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>79109</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1501,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497770</v>
+        <v>497686</v>
       </c>
       <c r="R9" t="n">
-        <v>6914222</v>
+        <v>6914152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118366174</v>
+        <v>118366870</v>
       </c>
       <c r="B10" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1613,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497751</v>
+        <v>497685</v>
       </c>
       <c r="R10" t="n">
-        <v>6914252</v>
+        <v>6914149</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118366020</v>
+        <v>118365298</v>
       </c>
       <c r="B11" t="n">
-        <v>90749</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,37 +1725,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497811</v>
+        <v>497786</v>
       </c>
       <c r="R11" t="n">
-        <v>6914303</v>
+        <v>6914375</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,7 +1812,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118365298</v>
+        <v>118365520</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>91786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,47 +1842,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497786</v>
+        <v>497776</v>
       </c>
       <c r="R12" t="n">
-        <v>6914375</v>
+        <v>6914369</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118366859</v>
+        <v>118366237</v>
       </c>
       <c r="B13" t="n">
-        <v>78221</v>
+        <v>79080</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1986,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497691</v>
+        <v>497770</v>
       </c>
       <c r="R13" t="n">
-        <v>6914141</v>
+        <v>6914222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118365226</v>
+        <v>118366020</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>90756</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2074,43 +2070,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497780</v>
+        <v>497811</v>
       </c>
       <c r="R14" t="n">
-        <v>6914401</v>
+        <v>6914303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2161,6 +2151,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2179,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118365427</v>
+        <v>118365226</v>
       </c>
       <c r="B15" t="n">
-        <v>78129</v>
+        <v>97853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,38 +2182,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497763</v>
+        <v>497780</v>
       </c>
       <c r="R15" t="n">
-        <v>6914373</v>
+        <v>6914401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118366870</v>
+        <v>118366174</v>
       </c>
       <c r="B16" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497685</v>
+        <v>497751</v>
       </c>
       <c r="R16" t="n">
-        <v>6914149</v>
+        <v>6914252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -1830,10 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118365520</v>
+        <v>118366237</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>79080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,25 +1842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497776</v>
+        <v>497770</v>
       </c>
       <c r="R12" t="n">
-        <v>6914369</v>
+        <v>6914222</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118366237</v>
+        <v>118365520</v>
       </c>
       <c r="B13" t="n">
-        <v>79080</v>
+        <v>91786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,25 +1954,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497770</v>
+        <v>497776</v>
       </c>
       <c r="R13" t="n">
-        <v>6914222</v>
+        <v>6914369</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118366889</v>
+        <v>118366859</v>
       </c>
       <c r="B3" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497668</v>
+        <v>497691</v>
       </c>
       <c r="R3" t="n">
-        <v>6914135</v>
+        <v>6914141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118366859</v>
+        <v>118365220</v>
       </c>
       <c r="B4" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,38 +928,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497691</v>
+        <v>497793</v>
       </c>
       <c r="R4" t="n">
-        <v>6914141</v>
+        <v>6914389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1140,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118365427</v>
+        <v>118366020</v>
       </c>
       <c r="B6" t="n">
-        <v>78136</v>
+        <v>90756</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1161,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497763</v>
+        <v>497811</v>
       </c>
       <c r="R6" t="n">
-        <v>6914373</v>
+        <v>6914303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,6 +1246,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118365220</v>
+        <v>118365226</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1287,7 +1300,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1301,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497793</v>
+        <v>497780</v>
       </c>
       <c r="R7" t="n">
-        <v>6914389</v>
+        <v>6914401</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118366558</v>
+        <v>118365520</v>
       </c>
       <c r="B8" t="n">
-        <v>78228</v>
+        <v>91786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497765</v>
+        <v>497776</v>
       </c>
       <c r="R8" t="n">
-        <v>6914163</v>
+        <v>6914369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118366628</v>
+        <v>118366889</v>
       </c>
       <c r="B9" t="n">
-        <v>79109</v>
+        <v>79080</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,21 +1514,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1525,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497686</v>
+        <v>497668</v>
       </c>
       <c r="R9" t="n">
-        <v>6914152</v>
+        <v>6914135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118366870</v>
+        <v>118365427</v>
       </c>
       <c r="B10" t="n">
-        <v>78227</v>
+        <v>78136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1626,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497685</v>
+        <v>497763</v>
       </c>
       <c r="R10" t="n">
-        <v>6914149</v>
+        <v>6914373</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118365298</v>
+        <v>118366870</v>
       </c>
       <c r="B11" t="n">
-        <v>97853</v>
+        <v>78227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,47 +1734,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497786</v>
+        <v>497685</v>
       </c>
       <c r="R11" t="n">
-        <v>6914375</v>
+        <v>6914149</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118366237</v>
+        <v>118366628</v>
       </c>
       <c r="B12" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1870,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497770</v>
+        <v>497686</v>
       </c>
       <c r="R12" t="n">
-        <v>6914222</v>
+        <v>6914152</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1942,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118365520</v>
+        <v>118366174</v>
       </c>
       <c r="B13" t="n">
-        <v>91786</v>
+        <v>78228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,25 +1958,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497776</v>
+        <v>497751</v>
       </c>
       <c r="R13" t="n">
-        <v>6914369</v>
+        <v>6914252</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118366020</v>
+        <v>118366558</v>
       </c>
       <c r="B14" t="n">
-        <v>90756</v>
+        <v>78228</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,41 +2070,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497811</v>
+        <v>497765</v>
       </c>
       <c r="R14" t="n">
-        <v>6914303</v>
+        <v>6914163</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2152,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2170,10 +2170,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118365226</v>
+        <v>118366237</v>
       </c>
       <c r="B15" t="n">
-        <v>97853</v>
+        <v>79080</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,47 +2182,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497780</v>
+        <v>497770</v>
       </c>
       <c r="R15" t="n">
-        <v>6914401</v>
+        <v>6914222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2291,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118366174</v>
+        <v>118365298</v>
       </c>
       <c r="B16" t="n">
-        <v>78228</v>
+        <v>97853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,38 +2294,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kronstugan (Kronstugan), Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497751</v>
+        <v>497786</v>
       </c>
       <c r="R16" t="n">
-        <v>6914252</v>
+        <v>6914375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 26314-2024 artfynd.xlsx
+++ b/artfynd/A 26314-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366020</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118365427</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118365520</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366628</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97022962</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118365220</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118365226</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118365298</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366103</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366174</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366558</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,6 +2166,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366859</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366237</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,8 +2390,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118366889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>